--- a/ExcelProject/RegisterTutor.xlsx
+++ b/ExcelProject/RegisterTutor.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Test-Tutor-main\ExcelProject\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC26202-929D-4F25-B69C-E1839D881FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12960" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="RegisterTutor "/>
+    <sheet name="RegisterTutor " sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="83">
   <si>
     <t>Execute</t>
   </si>
@@ -202,9 +208,6 @@
     <t>MJU6504106400</t>
   </si>
   <si>
-    <t>ฉันได้รับเกียรติให</t>
-  </si>
-  <si>
     <t>กรุณากรอกข้อมูลเป็นจำนวนไม่น้อยกว่า 20 ตัวอักษร และไม่เกิน 255 ตัวอักษร</t>
   </si>
   <si>
@@ -254,14 +257,25 @@
   </si>
   <si>
     <t>กรุณากรอกประสบการณ์</t>
+  </si>
+  <si>
+    <t>กรุณากรอกข้อมูลจำนวนไม่น้อยกว่า 4 ตัวอักษร และไม่เกิน 100 ตัวอักษร</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>ฉันได้รับเกียรติให้</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,14 +291,8 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFff0000"/>
+      <color rgb="FFFF0000"/>
       <name val="Angsana New"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -297,16 +305,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffffff"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFee0000"/>
+        <fgColor rgb="FFEE0000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -347,7 +355,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -375,65 +383,91 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -444,10 +478,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -485,71 +519,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -577,7 +611,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -600,11 +634,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -613,13 +647,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -629,7 +663,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -638,7 +672,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -647,7 +681,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -655,10 +689,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -723,26 +757,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="13" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="14" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="66.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="14" width="178.29071428571427" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="14" width="55.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="37.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="9.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="13" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="66.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="178.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.140625" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
+    <row r="1" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,7 +805,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
+    <row r="2" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -806,7 +837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="22.5">
+    <row r="3" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -838,7 +869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
+    <row r="4" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -870,7 +901,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
+    <row r="5" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -902,7 +933,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
+    <row r="6" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -934,7 +965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
+    <row r="7" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -966,7 +997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
+    <row r="8" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -998,9 +1029,9 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
+    <row r="9" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>39</v>
@@ -1018,21 +1049,25 @@
         <v>15</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
+        <v>26</v>
+      </c>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>42</v>
@@ -1050,19 +1085,23 @@
         <v>15</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
+        <v>26</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1092,7 +1131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
+    <row r="12" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1124,7 +1163,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="22.5">
+    <row r="13" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1156,7 +1195,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
+    <row r="14" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1188,7 +1227,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
+    <row r="15" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1220,7 +1259,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
+    <row r="16" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -1237,30 +1276,30 @@
         <v>14</v>
       </c>
       <c r="F16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="22.5">
-      <c r="A17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>13</v>
@@ -1269,10 +1308,10 @@
         <v>14</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>56</v>
@@ -1281,18 +1320,21 @@
         <v>26</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="22.5">
+        <v>26</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>13</v>
@@ -1301,7 +1343,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>16</v>
@@ -1316,15 +1358,15 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="21.75">
+    <row r="19" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>13</v>
@@ -1333,30 +1375,30 @@
         <v>14</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21.75">
-      <c r="A20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>13</v>
@@ -1365,7 +1407,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>16</v>
@@ -1380,15 +1422,15 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="22.5">
+    <row r="21" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>13</v>
@@ -1401,7 +1443,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>26</v>
